--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\etoga\マイドライブ（e.togashi@gmail.com）\研究\教育用環境計測デバイスの製作\git\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E064E88-1F85-4B40-9A65-A8CFD2D69647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B367B7F-C48A-4D9E-BD81-113EBF3DCEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47870" yWindow="7640" windowWidth="20150" windowHeight="12530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="5" r:id="rId1"/>
@@ -49,61 +49,18 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>TFPT1206L1002FV</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Manufacturer Part Number</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>ATmel</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Murata</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>VISHAY</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Panasonic</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Manufacturer</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GCJ188R71H104KA12D/2783803</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GRT188C80G105ME01J/13904968</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/vishay-dale/TFPT1206L1002FV/1427100</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>No.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Toshiba</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sensirion</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Same Sky (Formerly CUI Devices)</t>
-  </si>
-  <si>
     <t>AVR64DU32-I/RXB</t>
   </si>
   <si>
@@ -125,26 +82,6 @@
     <t>MCP6V02-E/MD</t>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/diotec-semiconductor/MMBT3904/13163698</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/CPF0603B2R21E1/14007137</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yageo Nexensos</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/yageo-nexensos/32208551/6677784</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/yageo/RC0603FR-074K7L/727212</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>PT1</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -153,26 +90,14 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J13KBTD/9480097</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>R7, R8</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J15KBTD/9480247</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>R5, R6</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J2K74BTD/9480545</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>R4</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -185,10 +110,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/yageo/RC0603FR-0710KL/726880</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>R1</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -201,34 +122,14 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/microchip-technology/MCP6V02-E-MD/1635826</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>O1</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/microchip-technology/AVR128DB32T-E-RXB/12807276</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>AVR128DB32</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>I3</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/toshiba-semiconductor-and-storage/TCR2EF20-LM-CT/5977733</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TCR2EF20,LM</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>I2</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -237,47 +138,15 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GRM188R60J476ME15D/5877410</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>C8</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>STCC4-D-R3</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/sensirion-ag/STCC4-D-R3/26769073</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
     <t>Spec</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>GCJ188R71H104KA12D</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>GRT188C80G105ME01J</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/texas-instruments/OPT3001DNPR/5039362</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Texas Instruments</t>
-  </si>
-  <si>
-    <t>OPT3001</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EXB-28V103JX</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -313,10 +182,6 @@
   <si>
     <t>47 uF</t>
     <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>GRM188R60J476ME15D</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>2.0 V</t>
@@ -366,66 +231,14 @@
     <phoneticPr fontId="19"/>
   </si>
   <si>
-    <t>RC0603FR-074K7L</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>RQ73C1J13KBTD</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>RQ73C1J15KBTD</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>RQ73C1J2K74BTD</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>RQ73C1J232RBTD</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>CPF0603B2R21E1</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>RC0603FR-0710KL</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHT40-AD1B</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.digikey.jp/ja/products/detail/sensirion-ag/SHT40-AD1B-R3/14322709</t>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/microchip-technology/AVR64DU32-I-RXB/22611635</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/same-sky-formerly-cui-devices/UJ20-C-H-G-MSMT-2-P16-TR/24818632</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/panasonic-electronic-components/EXB-28V103JX/256299</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>UJ20-C-H-G-MSMT-2-P16-TR</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>C1, C2, C3, C5, C9, C10, C11</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>C4, C6, C7</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TCR2EF33,LM</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -433,10 +246,6 @@
     <phoneticPr fontId="19"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/toshiba-semiconductor-and-storage/TCR2EF33-LM-CT/4503183</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
     <t>I4</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -462,8 +271,151 @@
     <phoneticPr fontId="19"/>
   </si>
   <si>
+    <t>Murata</t>
+  </si>
+  <si>
+    <t>GCJ188R71H104KA12D</t>
+  </si>
+  <si>
+    <t>GRT188C80G105ME01J</t>
+  </si>
+  <si>
+    <t>GRM188R60J476ME15D</t>
+  </si>
+  <si>
+    <t>Toshiba</t>
+  </si>
+  <si>
+    <t>TCR2EF33,LM</t>
+  </si>
+  <si>
+    <t>TCR2EF20,LM</t>
+  </si>
+  <si>
+    <t>ATmel</t>
+  </si>
+  <si>
+    <t>AVR128DB32T-E/RXB</t>
+  </si>
+  <si>
+    <t>OPT3001</t>
+  </si>
+  <si>
+    <t>Sensirion</t>
+  </si>
+  <si>
+    <t>SHT40-AD1B</t>
+  </si>
+  <si>
+    <t>STCC4-D-R3</t>
+  </si>
+  <si>
+    <t>Korean Hroparts Elec</t>
+  </si>
+  <si>
+    <t>TYPE-C-31-M-14</t>
+  </si>
+  <si>
+    <t>VISHAY</t>
+  </si>
+  <si>
+    <t>TFPT1206L1002FV</t>
+  </si>
+  <si>
     <t>Yageo</t>
-    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>RC0603FR-0710KL</t>
+  </si>
+  <si>
+    <t>CPF0603B2R21E1</t>
+  </si>
+  <si>
+    <t>RQ73C1J232RBTD</t>
+  </si>
+  <si>
+    <t>RQ73C1J2K74BTD</t>
+  </si>
+  <si>
+    <t>RQ73C1J15KBTD</t>
+  </si>
+  <si>
+    <t>RQ73C1J13KBTD</t>
+  </si>
+  <si>
+    <t>RC0603FR-074K7L</t>
+  </si>
+  <si>
+    <t>Panasonic</t>
+  </si>
+  <si>
+    <t>EXB-28V103JX</t>
+  </si>
+  <si>
+    <t>Yageo Nexensos</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GCJ188R71H104KA12D/2783803</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GRT188C80G105ME01J/13904968</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GRM188R60J476ME15D/5877410</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/toshiba-semiconductor-and-storage/TCR2EF33-LM-CT/4503183</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/toshiba-semiconductor-and-storage/TCR2EF20-LM-CT/5977733</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/microchip-technology/AVR128DB32T-E-RXB/12807276</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/microchip-technology/AVR64DU32-I-RXB/22611635</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/texas-instruments/OPT3001DNPR/5039362</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/sensirion-ag/STCC4-D-R3/26769073</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C223907.html</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/microchip-technology/MCP6V02-E-MD/1635826</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/vishay-dale/TFPT1206L1002FV/1427100</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/diotec-semiconductor/MMBT3904/13163698</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/yageo/RC0603FR-0710KL/726880</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/CPF0603B2R21E1/14007137</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J2K74BTD/9480545</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J15KBTD/9480247</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J13KBTD/9480097</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/yageo/RC0603FR-074K7L/727212</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/panasonic-electronic-components/EXB-28V103JX/256299</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/yageo-nexensos/32208551/6677784</t>
   </si>
 </sst>
 </file>
@@ -1550,7 +1502,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="11" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>0</v>
@@ -1559,13 +1511,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>2</v>
@@ -1576,23 +1528,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3">
         <f>LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.5">
@@ -1600,23 +1552,23 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C24" si="0">LEN(B3) - LEN(SUBSTITUTE(B3,",",""))+1</f>
         <v>3</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.5">
@@ -1624,23 +1576,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.5">
@@ -1648,23 +1600,23 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.5">
@@ -1672,23 +1624,23 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.5">
@@ -1696,21 +1648,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.5">
@@ -1718,21 +1670,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.5">
@@ -1740,21 +1692,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.5">
@@ -1762,21 +1714,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.5">
@@ -1784,23 +1736,23 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.5">
@@ -1808,23 +1760,23 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.5">
@@ -1832,21 +1784,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="10" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.5">
@@ -1854,21 +1806,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.5">
@@ -1876,21 +1828,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.5">
@@ -1898,23 +1850,23 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.5">
@@ -1922,23 +1874,23 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.5">
@@ -1946,23 +1898,23 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.5">
@@ -1970,23 +1922,23 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.5">
@@ -1994,23 +1946,23 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.5">
@@ -2018,23 +1970,23 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.5">
@@ -2042,23 +1994,23 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.5">
@@ -2066,23 +2018,23 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.5">
@@ -2090,21 +2042,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="E24" s="2">
         <v>32208551</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="2" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.5">

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\etoga\マイドライブ（e.togashi@gmail.com）\研究\教育用環境計測デバイスの製作\git\hardware\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_repositories\e-sensor\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B367B7F-C48A-4D9E-BD81-113EBF3DCEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A940DA1-C018-476B-9542-73DC303E5A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47870" yWindow="7640" windowWidth="20150" windowHeight="12530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="BOM" sheetId="5" r:id="rId1"/>
+    <sheet name="e_sensor" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">BOM!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">e_sensor!$A$1:$F$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="106">
   <si>
     <t>Designator</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -49,373 +49,409 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>TFPT1206L1002FV</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>Manufacturer Part Number</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>ATmel</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Murata</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>VISHAY</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panasonic</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>Manufacturer</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GCJ188R71H104KA12D/2783803</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/vishay-dale/TFPT1206L1002FV/1427100</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>No.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>Toshiba</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sensirion</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TE Connectivity Passive Product</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J232RBTD/9480531</t>
+  </si>
+  <si>
+    <t>Microchip Technology</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/diotec-semiconductor/MMBT3904/13163698</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/CPF0603B2R21E1/14007137</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yageo Nexensos</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/yageo-nexensos/32208551/6677784</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/yageo/RC0603FR-074K7L/727212</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PT1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>R9</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J13KBTD/9480097</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>R7, R8</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J15KBTD/9480247</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>R5, R6</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J2K74BTD/9480545</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>R4</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>R3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>R2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/microchip-technology/MCP6V02-E-MD/1635826</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>O1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/microchip-technology/AVR128DB32T-E-RXB/12807276</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>I3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>I2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>I1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GRM188R60J476ME15D/5877410</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>C8</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>STCC4-D-R3</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/sensirion-ag/STCC4-D-R3/26769073</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>Spec</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GCJ188R71H104KA12D</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/texas-instruments/OPT3001DNPR/5039362</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT3001</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXB-28V103JX</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type C</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1 uF</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>CO2</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>1 uF</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>47 uF</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>GRM188R60J476ME15D</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.0 V</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>232 Ω, 0.1%, 10ppm/C</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>2.74 kΩ, 0.1%, 10ppm/C</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>15 kΩ, 0.1%, 10ppm/C</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>13 kΩ, 0.1%, 10ppm/C</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>4.7 kΩ</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>RC0603FR-074K7L</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RQ73C1J13KBTD</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>RQ73C1J15KBTD</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>RQ73C1J2K74BTD</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>RQ73C1J232RBTD</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>CPF0603B2R21E1</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>SHT40-AD1B</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/sensirion-ag/SHT40-AD1B-R3/14322709</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/microchip-technology/AVR64DU32-I-RXB/22611635</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/panasonic-electronic-components/EXB-28V103JX/256299</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCR2EF33,LM</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.3 V</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/toshiba-semiconductor-and-storage/TCR2EF33-LM-CT/4503183</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>I4</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>I5</t>
+  </si>
+  <si>
+    <t>I6</t>
+  </si>
+  <si>
+    <t>I7</t>
+  </si>
+  <si>
+    <t>J1</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>RN1, RN2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10 kΩ</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>AVR128DB32T-E/RXB</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>AVR64DU32-I/RXB</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>MCP6V02-E/MD</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>MMBT3904</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>Korean Hroparts Elec</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TYPE-C-31-M-14</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C223907.html</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Texas Instruments</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>Diotec Semiconductor</t>
+    <phoneticPr fontId="19"/>
   </si>
   <si>
     <t>TE Connectivity Passive Product</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J232RBTD/9480531</t>
-  </si>
-  <si>
-    <t>Diotec Semiconductor</t>
-  </si>
-  <si>
-    <t>MMBT3904</t>
-  </si>
-  <si>
-    <t>Microchip Technology</t>
-  </si>
-  <si>
-    <t>MCP6V02-E/MD</t>
-  </si>
-  <si>
-    <t>PT1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>R9</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>R7, R8</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>R5, R6</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>R4</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>R3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>R2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>R1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Q1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>O1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>I3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>I2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>I1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>C8</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Spec</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Texas Instruments</t>
-  </si>
-  <si>
-    <r>
-      <t>10 k</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="161"/>
-      </rPr>
-      <t>Ω x 4</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Type C</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.1 uF</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>CO2</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>1 uF</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>47 uF</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>2.0 V</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">2.21 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="161"/>
-      </rPr>
-      <t>Ω</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>, 0.1%, 25ppm/C</t>
-    </r>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>232 Ω, 0.1%, 10ppm/C</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>2.74 kΩ, 0.1%, 10ppm/C</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>15 kΩ, 0.1%, 10ppm/C</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>13 kΩ, 0.1%, 10ppm/C</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>4.7 kΩ</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/sensirion-ag/SHT40-AD1B-R3/14322709</t>
-  </si>
-  <si>
-    <t>C1, C2, C3, C5, C9, C10, C11</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>C4, C6, C7</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.3 V</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>I4</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>I5</t>
-  </si>
-  <si>
-    <t>I6</t>
-  </si>
-  <si>
-    <t>I7</t>
-  </si>
-  <si>
-    <t>J1</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>RN1, RN2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>10 kΩ</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>Murata</t>
-  </si>
-  <si>
-    <t>GCJ188R71H104KA12D</t>
-  </si>
-  <si>
-    <t>GRT188C80G105ME01J</t>
-  </si>
-  <si>
-    <t>GRM188R60J476ME15D</t>
-  </si>
-  <si>
-    <t>Toshiba</t>
-  </si>
-  <si>
-    <t>TCR2EF33,LM</t>
-  </si>
-  <si>
-    <t>TCR2EF20,LM</t>
-  </si>
-  <si>
-    <t>ATmel</t>
-  </si>
-  <si>
-    <t>AVR128DB32T-E/RXB</t>
-  </si>
-  <si>
-    <t>OPT3001</t>
-  </si>
-  <si>
-    <t>Sensirion</t>
-  </si>
-  <si>
-    <t>SHT40-AD1B</t>
-  </si>
-  <si>
-    <t>STCC4-D-R3</t>
-  </si>
-  <si>
-    <t>Korean Hroparts Elec</t>
-  </si>
-  <si>
-    <t>TYPE-C-31-M-14</t>
-  </si>
-  <si>
-    <t>VISHAY</t>
-  </si>
-  <si>
-    <t>TFPT1206L1002FV</t>
+    <phoneticPr fontId="19"/>
   </si>
   <si>
     <t>Yageo</t>
-  </si>
-  <si>
-    <t>RC0603FR-0710KL</t>
-  </si>
-  <si>
-    <t>CPF0603B2R21E1</t>
-  </si>
-  <si>
-    <t>RQ73C1J232RBTD</t>
-  </si>
-  <si>
-    <t>RQ73C1J2K74BTD</t>
-  </si>
-  <si>
-    <t>RQ73C1J15KBTD</t>
-  </si>
-  <si>
-    <t>RQ73C1J13KBTD</t>
-  </si>
-  <si>
-    <t>RC0603FR-074K7L</t>
-  </si>
-  <si>
-    <t>Panasonic</t>
-  </si>
-  <si>
-    <t>EXB-28V103JX</t>
-  </si>
-  <si>
-    <t>Yageo Nexensos</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GCJ188R71H104KA12D/2783803</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GRT188C80G105ME01J/13904968</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GRM188R60J476ME15D/5877410</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/toshiba-semiconductor-and-storage/TCR2EF33-LM-CT/4503183</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/toshiba-semiconductor-and-storage/TCR2EF20-LM-CT/5977733</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/microchip-technology/AVR128DB32T-E-RXB/12807276</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/microchip-technology/AVR64DU32-I-RXB/22611635</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/texas-instruments/OPT3001DNPR/5039362</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/sensirion-ag/STCC4-D-R3/26769073</t>
-  </si>
-  <si>
-    <t>https://www.lcsc.com/product-detail/C223907.html</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/microchip-technology/MCP6V02-E-MD/1635826</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/vishay-dale/TFPT1206L1002FV/1427100</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/diotec-semiconductor/MMBT3904/13163698</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/yageo/RC0603FR-0710KL/726880</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/CPF0603B2R21E1/14007137</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J2K74BTD/9480545</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J15KBTD/9480247</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J13KBTD/9480097</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/yageo/RC0603FR-074K7L/727212</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/panasonic-electronic-components/EXB-28V103JX/256299</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/yageo-nexensos/32208551/6677784</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>UNI-ROYAL(Uniroyal Elec)</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>0603WAF1002T5E</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/26547-0603WAF1002T5E/C25804</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Samsung Electro-Mechanics</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>CL10A105KB8NNNC</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/16531-CL10A105KB8NNNC/C15849</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>C2, C3, C5, C9, C10, C11</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCR3UF20A,LM(CT</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C7067134.html</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>C1, C4, C6, C7</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.21 Ω, 0.1%, 25ppm/C</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>10 kΩ x 4</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -426,7 +462,7 @@
     <numFmt numFmtId="6" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
     <numFmt numFmtId="176" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -609,18 +645,6 @@
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="ＭＳ ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="161"/>
     </font>
     <font>
       <sz val="13"/>
@@ -1124,11 +1148,11 @@
     <xf numFmtId="0" fontId="21" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1487,7 +1511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5AA7A7-E5B5-43A4-83E6-13376124CF67}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="3.7265625" style="7" bestFit="1" customWidth="1"/>
@@ -1496,13 +1520,13 @@
     <col min="4" max="4" width="38.26953125" style="9" customWidth="1"/>
     <col min="5" max="5" width="22.6328125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.1328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="94.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.7265625" style="8" customWidth="1"/>
     <col min="8" max="16384" width="11" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" ht="16.2" x14ac:dyDescent="0.5">
       <c r="A1" s="11" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>0</v>
@@ -1511,578 +1535,565 @@
         <v>1</v>
       </c>
       <c r="D1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="11" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="12" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A2" s="6">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="C2" s="3">
         <f>LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A3" s="6">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C24" si="0">LEN(B3) - LEN(SUBSTITUTE(B3,",",""))+1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A4" s="6">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A5" s="6">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A7" s="6">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A8" s="6">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.5">
+        <v>71</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A9" s="6">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.5">
+        <v>48</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A10" s="6">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.5">
+        <v>70</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A11" s="6">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.5">
+        <v>45</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A12" s="6">
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
+        <v>89</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A13" s="6">
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A14" s="6">
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A15" s="6">
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A16" s="6">
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>72</v>
+      <c r="D16" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>95</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A17" s="6">
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A18" s="6">
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A19" s="6">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A20" s="6">
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A21" s="6">
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A22" s="6">
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A23" s="6">
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.5">
+        <v>72</v>
+      </c>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A24" s="6">
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2">
         <v>32208551</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="F26" s="8"/>
-      <c r="G26" s="13"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="F27" s="8"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="F28" s="8"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="F29" s="8"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="F30" s="8"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="F31" s="8"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="F32" s="8"/>
-    </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.5">
-      <c r="F33" s="8"/>
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="19"/>

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_repositories\e-sensor\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A940DA1-C018-476B-9542-73DC303E5A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F674122-3763-4442-B7C7-7D59C783D506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="107">
   <si>
     <t>Designator</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -77,10 +77,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GCJ188R71H104KA12D/2783803</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.digikey.jp/ja/products/detail/vishay-dale/TFPT1206L1002FV/1427100</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -106,10 +102,6 @@
     <t>Microchip Technology</t>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/diotec-semiconductor/MMBT3904/13163698</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/CPF0603B2R21E1/14007137</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -122,10 +114,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/yageo/RC0603FR-074K7L/727212</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>PT1</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -222,10 +210,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>GCJ188R71H104KA12D</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.digikey.jp/ja/products/detail/texas-instruments/OPT3001DNPR/5039362</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -286,10 +270,6 @@
     <phoneticPr fontId="19"/>
   </si>
   <si>
-    <t>RC0603FR-074K7L</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>RQ73C1J13KBTD</t>
     <phoneticPr fontId="19"/>
   </si>
@@ -374,10 +354,6 @@
     <phoneticPr fontId="19"/>
   </si>
   <si>
-    <t>MMBT3904</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
     <t>Korean Hroparts Elec</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -394,18 +370,10 @@
     <phoneticPr fontId="19"/>
   </si>
   <si>
-    <t>Diotec Semiconductor</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
     <t>TE Connectivity Passive Product</t>
     <phoneticPr fontId="19"/>
   </si>
   <si>
-    <t>Yageo</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
     <t>UNI-ROYAL(Uniroyal Elec)</t>
     <phoneticPr fontId="19"/>
   </si>
@@ -430,10 +398,6 @@
     <phoneticPr fontId="19"/>
   </si>
   <si>
-    <t>C2, C3, C5, C9, C10, C11</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>TCR3UF20A,LM(CT</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -442,15 +406,71 @@
     <phoneticPr fontId="19"/>
   </si>
   <si>
-    <t>C1, C4, C6, C7</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>2.21 Ω, 0.1%, 25ppm/C</t>
     <phoneticPr fontId="19"/>
   </si>
   <si>
     <t>10 kΩ x 4</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>YAGEO</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>CC0603KRX7R9BB104</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C14663.html</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C20526.html</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>JSCJ</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>JSCJ MMBT3904(RANGE:100-300)</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>0603WAF4701T5E</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNI-ROYAL</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C23162.html</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>C4, C6, C7</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">C1, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C2, C3, C5, C9, C10, C11</t>
+    </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1117,7 +1137,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1153,6 +1173,12 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1526,7 +1552,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="16.2" x14ac:dyDescent="0.5">
       <c r="A1" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>0</v>
@@ -1541,7 +1567,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>2</v>
@@ -1552,23 +1578,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C2" s="3">
         <f>LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>10</v>
+        <v>48</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.5">
@@ -1576,23 +1602,23 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C24" si="0">LEN(B3) - LEN(SUBSTITUTE(B3,",",""))+1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.5">
@@ -1600,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="0"/>
@@ -1610,13 +1636,13 @@
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.5">
@@ -1624,23 +1650,23 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.5">
@@ -1648,23 +1674,23 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.5">
@@ -1672,7 +1698,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="0"/>
@@ -1682,11 +1708,11 @@
         <v>5</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.5">
@@ -1694,7 +1720,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="0"/>
@@ -1704,11 +1730,11 @@
         <v>5</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -1718,21 +1744,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
@@ -1742,21 +1768,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -1766,23 +1792,23 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
@@ -1792,23 +1818,23 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -1818,21 +1844,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.5">
@@ -1840,7 +1866,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="0"/>
@@ -1854,7 +1880,7 @@
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.5">
@@ -1862,21 +1888,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>86</v>
+      <c r="D15" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>101</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="2" t="s">
-        <v>18</v>
+      <c r="G15" s="14" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.5">
@@ -1884,23 +1910,23 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.5">
@@ -1908,23 +1934,23 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.5">
@@ -1932,23 +1958,23 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.5">
@@ -1956,23 +1982,23 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.5">
@@ -1980,23 +2006,23 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.5">
@@ -2004,23 +2030,23 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.5">
@@ -2028,23 +2054,23 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D22" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>63</v>
+      <c r="D22" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>102</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>22</v>
+        <v>58</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
@@ -2052,7 +2078,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="0"/>
@@ -2062,13 +2088,13 @@
         <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -2078,21 +2104,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E24" s="2">
         <v>32208551</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_repositories\e-sensor\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F674122-3763-4442-B7C7-7D59C783D506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6B347E-17A7-4419-94DF-B719D9ED5747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41160" yWindow="1400" windowWidth="26860" windowHeight="14360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="e_sensor" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">e_sensor!$A$1:$F$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">e_sensor!$A$1:$F$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="109">
   <si>
     <t>Designator</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -411,18 +411,6 @@
   </si>
   <si>
     <t>10 kΩ x 4</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>YAGEO</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>CC0603KRX7R9BB104</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.lcsc.com/product-detail/C14663.html</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -472,6 +460,25 @@
       <t>C2, C3, C5, C9, C10, C11</t>
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>CL05B104KO5NNNC</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>I8</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C1525.html</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C122837.html</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>TPS22965DSGR</t>
   </si>
 </sst>
 </file>
@@ -1137,7 +1144,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1179,6 +1186,15 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1537,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5AA7A7-E5B5-43A4-83E6-13376124CF67}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="3.7265625" style="7" bestFit="1" customWidth="1"/>
@@ -1578,23 +1594,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C2" s="3">
         <f>LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
         <v>7</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>48</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.5">
@@ -1602,10 +1618,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C3" s="3">
-        <f t="shared" ref="C3:C24" si="0">LEN(B3) - LEN(SUBSTITUTE(B3,",",""))+1</f>
+        <f t="shared" ref="C3:C25" si="0">LEN(B3) - LEN(SUBSTITUTE(B3,",",""))+1</f>
         <v>3</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1813,74 +1829,76 @@
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
     </row>
-    <row r="12" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="6">
+    <row r="12" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="17">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="3">
+      <c r="B12" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="18">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>83</v>
+      <c r="D12" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14" t="s">
+        <v>107</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A13" s="6">
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="10" t="s">
-        <v>33</v>
-      </c>
+      <c r="D13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A14" s="6">
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>3</v>
+      <c r="D14" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>80</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="2" t="s">
-        <v>10</v>
+      <c r="G14" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.5">
@@ -1888,21 +1906,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>101</v>
+      <c r="D15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="14" t="s">
-        <v>99</v>
+      <c r="G15" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.5">
@@ -1910,23 +1928,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>88</v>
+      <c r="D16" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="14" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.5">
@@ -1934,23 +1950,23 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>63</v>
+      <c r="D17" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.5">
@@ -1958,23 +1974,23 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.5">
@@ -1982,23 +1998,23 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.5">
@@ -2006,23 +2022,23 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.5">
@@ -2030,7 +2046,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="0"/>
@@ -2040,13 +2056,13 @@
         <v>14</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.5">
@@ -2054,72 +2070,99 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
+        <v>2</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A23" s="6">
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.5">
+        <v>1</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A24" s="6">
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A25" s="6">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E25" s="2">
         <v>32208551</v>
       </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="2" t="s">
+      <c r="F25" s="5"/>
+      <c r="G25" s="2" t="s">
         <v>19</v>
       </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="E27" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19"/>

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_repositories\e-sensor\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6B347E-17A7-4419-94DF-B719D9ED5747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D77B6E-CC53-434E-AE4D-9BD031A3F728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41160" yWindow="1400" windowWidth="26860" windowHeight="14360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44790" yWindow="1500" windowWidth="31010" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="e_sensor" sheetId="5" r:id="rId1"/>
@@ -479,6 +479,7 @@
   </si>
   <si>
     <t>TPS22965DSGR</t>
+    <phoneticPr fontId="19"/>
   </si>
 </sst>
 </file>

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_repositories\e-sensor\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D77B6E-CC53-434E-AE4D-9BD031A3F728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD72C2D7-2DC6-4F8D-8EB6-8FED5D9D12C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44790" yWindow="1500" windowWidth="31010" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="e_sensor" sheetId="5" r:id="rId1"/>

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_repositories\e-sensor\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD72C2D7-2DC6-4F8D-8EB6-8FED5D9D12C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46BB2EB6-D618-45D5-BC07-506BFA7705FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="58020" yWindow="4150" windowWidth="17560" windowHeight="14800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="e_sensor" sheetId="5" r:id="rId1"/>

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_repositories\e-sensor\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46BB2EB6-D618-45D5-BC07-506BFA7705FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D45B72-2DB8-4344-B67D-85CA4B0F945B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58020" yWindow="4150" windowWidth="17560" windowHeight="14800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="726" yWindow="468" windowWidth="20226" windowHeight="11286" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="e_sensor" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">e_sensor!$A$1:$F$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">e_sensor!$A$1:$F$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="104">
   <si>
     <t>Designator</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -154,10 +154,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>R1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Q1</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -338,10 +334,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>10 kΩ</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
     <t>AVR128DB32T-E/RXB</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -374,18 +366,6 @@
     <phoneticPr fontId="19"/>
   </si>
   <si>
-    <t>UNI-ROYAL(Uniroyal Elec)</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>0603WAF1002T5E</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://jlcpcb.com/partdetail/26547-0603WAF1002T5E/C25804</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Samsung Electro-Mechanics</t>
     <phoneticPr fontId="19"/>
   </si>
@@ -442,26 +422,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">C1, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>C2, C3, C5, C9, C10, C11</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>CL05B104KO5NNNC</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -480,6 +440,10 @@
   <si>
     <t>TPS22965DSGR</t>
     <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>C1, C2, C3, C5, C9, C10, C11</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1145,7 +1109,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1179,23 +1143,8 @@
     <xf numFmtId="0" fontId="23" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1554,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5AA7A7-E5B5-43A4-83E6-13376124CF67}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="3.7265625" style="7" bestFit="1" customWidth="1"/>
@@ -1584,7 +1533,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>2</v>
@@ -1601,17 +1550,17 @@
         <f>LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
         <v>7</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>104</v>
+      <c r="D2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>106</v>
+        <v>47</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.5">
@@ -1619,23 +1568,23 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C3" s="3">
-        <f t="shared" ref="C3:C25" si="0">LEN(B3) - LEN(SUBSTITUTE(B3,",",""))+1</f>
+        <f t="shared" ref="C3:C24" si="0">LEN(B3) - LEN(SUBSTITUTE(B3,",",""))+1</f>
         <v>3</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.5">
@@ -1643,7 +1592,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="0"/>
@@ -1653,13 +1602,13 @@
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.5">
@@ -1667,7 +1616,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="0"/>
@@ -1677,13 +1626,13 @@
         <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.5">
@@ -1691,7 +1640,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="0"/>
@@ -1701,13 +1650,13 @@
         <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.5">
@@ -1715,7 +1664,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="0"/>
@@ -1725,11 +1674,11 @@
         <v>5</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.5">
@@ -1737,7 +1686,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="0"/>
@@ -1747,11 +1696,11 @@
         <v>5</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -1761,21 +1710,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
@@ -1785,7 +1734,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="0"/>
@@ -1795,11 +1744,11 @@
         <v>13</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -1809,7 +1758,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="0"/>
@@ -1819,37 +1768,37 @@
         <v>13</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="17">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="18">
+      <c r="B12" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14" t="s">
-        <v>107</v>
+      <c r="D12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -1859,23 +1808,23 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>83</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
@@ -1885,7 +1834,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="0"/>
@@ -1895,11 +1844,11 @@
         <v>16</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.5">
@@ -1907,7 +1856,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="0"/>
@@ -1929,21 +1878,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>98</v>
+      <c r="D16" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="14" t="s">
-        <v>96</v>
+      <c r="G16" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.5">
@@ -1951,23 +1900,23 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>87</v>
+      <c r="D17" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.5">
@@ -1975,23 +1924,23 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.5">
@@ -1999,23 +1948,23 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>54</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.5">
@@ -2023,23 +1972,23 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.5">
@@ -2047,7 +1996,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="0"/>
@@ -2057,13 +2006,13 @@
         <v>14</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.5">
@@ -2071,99 +2020,75 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>57</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A23" s="6">
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A24" s="6">
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>95</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E24" s="2">
+        <v>32208551</v>
+      </c>
+      <c r="F24" s="5"/>
       <c r="G24" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="A25" s="6">
-        <v>24</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="2">
-        <v>32208551</v>
-      </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="E27" s="16"/>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="E26" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19"/>

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_repositories\e-sensor\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D45B72-2DB8-4344-B67D-85CA4B0F945B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95543147-04F5-4BDC-93B6-383D0AB18A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="726" yWindow="468" windowWidth="20226" windowHeight="11286" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6048" yWindow="0" windowWidth="17280" windowHeight="8904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="e_sensor" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">e_sensor!$A$1:$F$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">e_sensor!$A$1:$G$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="106">
   <si>
     <t>Designator</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -444,6 +444,14 @@
   <si>
     <t>C1, C2, C3, C5, C9, C10, C11</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoHS</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="19"/>
   </si>
 </sst>
 </file>
@@ -1503,7 +1511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5AA7A7-E5B5-43A4-83E6-13376124CF67}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="3.7265625" style="7" bestFit="1" customWidth="1"/>
@@ -1512,11 +1520,12 @@
     <col min="4" max="4" width="38.26953125" style="9" customWidth="1"/>
     <col min="5" max="5" width="22.6328125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.1328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.7265625" style="8" customWidth="1"/>
-    <col min="8" max="16384" width="11" style="7"/>
+    <col min="7" max="7" width="6.40625" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.7265625" style="8" customWidth="1"/>
+    <col min="9" max="16384" width="11" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" ht="16.2" x14ac:dyDescent="0.5">
       <c r="A1" s="11" t="s">
         <v>11</v>
       </c>
@@ -1535,11 +1544,14 @@
       <c r="F1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -1559,11 +1571,14 @@
       <c r="F2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -1583,11 +1598,14 @@
       <c r="F3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -1607,11 +1625,14 @@
       <c r="F4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -1631,11 +1652,14 @@
       <c r="F5" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -1655,11 +1679,14 @@
       <c r="F6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -1677,11 +1704,14 @@
         <v>76</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -1699,13 +1729,16 @@
         <v>77</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="7"/>
       <c r="I8" s="7"/>
-    </row>
-    <row r="9" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="J8" s="7"/>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -1723,13 +1756,16 @@
         <v>44</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="7"/>
       <c r="I9" s="7"/>
-    </row>
-    <row r="10" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="J9" s="7"/>
+    </row>
+    <row r="10" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -1747,13 +1783,16 @@
         <v>63</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H10" s="7"/>
       <c r="I10" s="7"/>
-    </row>
-    <row r="11" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="J10" s="7"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -1773,13 +1812,16 @@
       <c r="F11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="7"/>
       <c r="I11" s="7"/>
-    </row>
-    <row r="12" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="J11" s="7"/>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A12" s="6">
         <v>11</v>
       </c>
@@ -1797,13 +1839,16 @@
         <v>102</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="H12" s="7"/>
       <c r="I12" s="7"/>
-    </row>
-    <row r="13" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="J12" s="7"/>
+    </row>
+    <row r="13" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -1823,13 +1868,16 @@
       <c r="F13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H13" s="7"/>
       <c r="I13" s="7"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A14" s="6">
         <v>13</v>
       </c>
@@ -1847,11 +1895,14 @@
         <v>78</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H14" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -1869,11 +1920,14 @@
         <v>3</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A16" s="6">
         <v>15</v>
       </c>
@@ -1891,11 +1945,14 @@
         <v>93</v>
       </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -1915,11 +1972,14 @@
       <c r="F17" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A18" s="6">
         <v>17</v>
       </c>
@@ -1939,11 +1999,14 @@
       <c r="F18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -1963,11 +2026,14 @@
       <c r="F19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A20" s="6">
         <v>19</v>
       </c>
@@ -1987,11 +2053,14 @@
       <c r="F20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -2011,11 +2080,14 @@
       <c r="F21" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A22" s="6">
         <v>21</v>
       </c>
@@ -2035,11 +2107,14 @@
       <c r="F22" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -2059,13 +2134,16 @@
       <c r="F23" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H23" s="7"/>
       <c r="I23" s="7"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J23" s="7"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A24" s="6">
         <v>23</v>
       </c>
@@ -2083,11 +2161,14 @@
         <v>32208551</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.5">
       <c r="E26" s="13"/>
     </row>
   </sheetData>
